--- a/Assets/Excel/Monster.xlsx
+++ b/Assets/Excel/Monster.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14970" windowHeight="6930"/>
+    <workbookView windowWidth="18765" windowHeight="7530"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="59">
   <si>
     <t>type</t>
   </si>
@@ -203,6 +203,9 @@
   </si>
   <si>
     <t>月晶石（巨型）</t>
+  </si>
+  <si>
+    <t>金元宝</t>
   </si>
 </sst>
 </file>
@@ -831,8 +834,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1145,20 +1148,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="11.375" customWidth="1"/>
     <col min="4" max="4" width="10.75" customWidth="1"/>
+    <col min="5" max="5" width="11.7333333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -1167,7 +1171,7 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1175,7 +1179,7 @@
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -1184,7 +1188,7 @@
       <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1192,7 +1196,7 @@
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -1209,7 +1213,7 @@
       <c r="A4" s="1">
         <v>1</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C4" s="1">
@@ -1243,7 +1247,7 @@
       <c r="A6" s="1">
         <v>3</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C6" s="1">
@@ -1260,7 +1264,7 @@
       <c r="A7" s="1">
         <v>4</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C7" s="1">
@@ -1277,7 +1281,7 @@
       <c r="A8" s="1">
         <v>5</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C8" s="1">
@@ -1294,7 +1298,7 @@
       <c r="A9" s="1">
         <v>6</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C9" s="1">
@@ -1311,7 +1315,7 @@
       <c r="A10" s="1">
         <v>7</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C10" s="1">
@@ -1328,7 +1332,7 @@
       <c r="A11" s="1">
         <v>8</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C11" s="1">
@@ -1345,7 +1349,7 @@
       <c r="A12" s="1">
         <v>9</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C12" s="1">
@@ -1362,7 +1366,7 @@
       <c r="A13" s="1">
         <v>10</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C13" s="1">
@@ -1379,7 +1383,7 @@
       <c r="A14" s="1">
         <v>11</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C14" s="1">
@@ -1396,7 +1400,7 @@
       <c r="A15" s="1">
         <v>12</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C15" s="1">
@@ -1413,7 +1417,7 @@
       <c r="A16" s="1">
         <v>13</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C16" s="1">
@@ -1430,7 +1434,7 @@
       <c r="A17" s="1">
         <v>14</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C17" s="1">
@@ -1447,7 +1451,7 @@
       <c r="A18" s="1">
         <v>15</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C18" s="1">
@@ -1464,7 +1468,7 @@
       <c r="A19" s="1">
         <v>16</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C19" s="1">
@@ -1481,7 +1485,7 @@
       <c r="A20" s="1">
         <v>17</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="1" t="s">
         <v>29</v>
       </c>
       <c r="C20" s="1">
@@ -1498,7 +1502,7 @@
       <c r="A21" s="1">
         <v>18</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C21" s="1">
@@ -1515,7 +1519,7 @@
       <c r="A22" s="1">
         <v>19</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="1" t="s">
         <v>31</v>
       </c>
       <c r="C22" s="1">
@@ -1532,7 +1536,7 @@
       <c r="A23" s="1">
         <v>20</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C23" s="1">
@@ -1549,7 +1553,7 @@
       <c r="A24" s="1">
         <v>21</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C24" s="1">
@@ -1566,7 +1570,7 @@
       <c r="A25" s="1">
         <v>22</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="1" t="s">
         <v>34</v>
       </c>
       <c r="C25" s="1">
@@ -1583,7 +1587,7 @@
       <c r="A26" s="1">
         <v>23</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C26" s="1">
@@ -1600,7 +1604,7 @@
       <c r="A27" s="1">
         <v>24</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="1" t="s">
         <v>36</v>
       </c>
       <c r="C27" s="1">
@@ -1617,7 +1621,7 @@
       <c r="A28" s="1">
         <v>25</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C28" s="1">
@@ -1634,7 +1638,7 @@
       <c r="A29" s="1">
         <v>26</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="1" t="s">
         <v>38</v>
       </c>
       <c r="C29" s="1">
@@ -1651,7 +1655,7 @@
       <c r="A30" s="1">
         <v>27</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C30" s="1">
@@ -1668,7 +1672,7 @@
       <c r="A31" s="1">
         <v>28</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="1" t="s">
         <v>40</v>
       </c>
       <c r="C31" s="1">
@@ -1685,7 +1689,7 @@
       <c r="A32" s="1">
         <v>29</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C32" s="1">
@@ -1702,7 +1706,7 @@
       <c r="A33" s="1">
         <v>30</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C33" s="1">
@@ -1719,7 +1723,7 @@
       <c r="A34" s="1">
         <v>31</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="1" t="s">
         <v>43</v>
       </c>
       <c r="C34" s="1">
@@ -1736,7 +1740,7 @@
       <c r="A35" s="1">
         <v>32</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C35" s="1">
@@ -1753,7 +1757,7 @@
       <c r="A36" s="1">
         <v>33</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C36" s="1">
@@ -1770,7 +1774,7 @@
       <c r="A37" s="1">
         <v>34</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="1" t="s">
         <v>46</v>
       </c>
       <c r="C37" s="1">
@@ -1787,7 +1791,7 @@
       <c r="A38" s="1">
         <v>35</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C38" s="1">
@@ -1804,7 +1808,7 @@
       <c r="A39" s="1">
         <v>36</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C39" s="1">
@@ -1821,7 +1825,7 @@
       <c r="A40" s="1">
         <v>37</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C40" s="1">
@@ -1838,7 +1842,7 @@
       <c r="A41" s="1">
         <v>38</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C41" s="1">
@@ -1855,7 +1859,7 @@
       <c r="A42" s="1">
         <v>39</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="1" t="s">
         <v>51</v>
       </c>
       <c r="C42" s="1">
@@ -1872,7 +1876,7 @@
       <c r="A43" s="1">
         <v>40</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="1" t="s">
         <v>52</v>
       </c>
       <c r="C43" s="1">
@@ -1889,7 +1893,7 @@
       <c r="A44" s="1">
         <v>41</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C44" s="1">
@@ -1906,7 +1910,7 @@
       <c r="A45" s="1">
         <v>42</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="1" t="s">
         <v>54</v>
       </c>
       <c r="C45" s="1">
@@ -1923,7 +1927,7 @@
       <c r="A46" s="1">
         <v>43</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="1" t="s">
         <v>55</v>
       </c>
       <c r="C46" s="1">
@@ -1940,7 +1944,7 @@
       <c r="A47" s="1">
         <v>44</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="1" t="s">
         <v>56</v>
       </c>
       <c r="C47" s="1">
@@ -1957,7 +1961,7 @@
       <c r="A48" s="1">
         <v>45</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C48" s="1">
@@ -1968,6 +1972,23 @@
       </c>
       <c r="E48" s="1">
         <v>20</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="1">
+        <v>46</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C49" s="1">
+        <v>10</v>
+      </c>
+      <c r="D49" s="1">
+        <v>8</v>
+      </c>
+      <c r="E49" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
